--- a/docs/all/idx4_Capacidad_loadings_y_tops.xlsx
+++ b/docs/all/idx4_Capacidad_loadings_y_tops.xlsx
@@ -396,10 +396,10 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.244981372542498</v>
+        <v>0.2449813725424976</v>
       </c>
       <c r="D2">
-        <v>0.1516071474535252</v>
+        <v>0.151607147453525</v>
       </c>
       <c r="E2">
         <v>15.2</v>
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.6736089653647673</v>
+        <v>0.6736089653647666</v>
       </c>
       <c r="D3">
-        <v>0.4168640769630635</v>
+        <v>0.416864076963063</v>
       </c>
       <c r="E3">
         <v>41.7</v>
@@ -438,10 +438,10 @@
         </is>
       </c>
       <c r="C4">
-        <v>0.6973055921813635</v>
+        <v>0.6973055921813647</v>
       </c>
       <c r="D4">
-        <v>0.4315287755834112</v>
+        <v>0.431528775583412</v>
       </c>
       <c r="E4">
         <v>43.2</v>
@@ -459,7 +459,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>0.9590581089144214</v>
+        <v>0.9590581089144219</v>
       </c>
       <c r="D5">
         <v>0.7347393644371455</v>
@@ -480,10 +480,10 @@
         </is>
       </c>
       <c r="C6">
-        <v>-0.2737819226153607</v>
+        <v>-0.2737819226153604</v>
       </c>
       <c r="D6">
-        <v>0.2097457431901445</v>
+        <v>0.2097457431901442</v>
       </c>
       <c r="E6">
         <v>21</v>
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="C7">
-        <v>-0.0724638018222223</v>
+        <v>-0.07246380182222273</v>
       </c>
       <c r="D7">
-        <v>0.05551489237270999</v>
+        <v>0.05551489237271029</v>
       </c>
       <c r="E7">
         <v>5.6</v>
@@ -525,7 +525,7 @@
         <v>0.1420973991059915</v>
       </c>
       <c r="D8">
-        <v>0.09216882226132428</v>
+        <v>0.09216882226132424</v>
       </c>
       <c r="E8">
         <v>9.199999999999999</v>
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="C9">
-        <v>0.6865088642029648</v>
+        <v>0.686508864202966</v>
       </c>
       <c r="D9">
-        <v>0.4452911445504331</v>
+        <v>0.4452911445504338</v>
       </c>
       <c r="E9">
         <v>44.5</v>
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="C10">
-        <v>-0.7131016116501686</v>
+        <v>-0.7131016116501678</v>
       </c>
       <c r="D10">
-        <v>0.4625400331882426</v>
+        <v>0.462540033188242</v>
       </c>
       <c r="E10">
         <v>46.3</v>
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.4658928480811765</v>
+        <v>0.4658928480811764</v>
       </c>
     </row>
     <row r="3">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.3274650893458441</v>
+        <v>0.3274650893458443</v>
       </c>
     </row>
     <row r="4">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.6973055921813635</v>
+        <v>0.6973055921813647</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.6736089653647673</v>
+        <v>0.6736089653647666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.244981372542498</v>
+        <v>0.2449813725424976</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.9590581089144214</v>
+        <v>0.9590581089144219</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.2737819226153607</v>
+        <v>-0.2737819226153604</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.0724638018222223</v>
+        <v>-0.07246380182222273</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
